--- a/artfynd/A 54017-2023 artfynd.xlsx
+++ b/artfynd/A 54017-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54017-2023 artfynd.xlsx
+++ b/artfynd/A 54017-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>113722383</v>
       </c>
       <c r="B17" t="n">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 54017-2023 artfynd.xlsx
+++ b/artfynd/A 54017-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113563373</v>
+        <v>113722393</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnaretjärnet (Gunnaretjärnet), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352393</v>
+        <v>352372</v>
       </c>
       <c r="R2" t="n">
-        <v>6580236</v>
+        <v>6579963</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,30 +762,26 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113563389</v>
+        <v>113722409</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +789,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnaretjärnet (Gunnaretjärnet), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352394</v>
+        <v>352428</v>
       </c>
       <c r="R3" t="n">
-        <v>6580301</v>
+        <v>6580131</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +843,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,30 +865,26 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113563468</v>
+        <v>113722454</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,44 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myggedalen (Myggedalen), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>352554</v>
+        <v>352310</v>
       </c>
       <c r="R4" t="n">
-        <v>6580561</v>
+        <v>6580464</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,27 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hördes</t>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,30 +968,26 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113563144</v>
+        <v>113722459</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,47 +995,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stutögat (Stutögat), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352367</v>
+        <v>352309</v>
       </c>
       <c r="R5" t="n">
-        <v>6579883</v>
+        <v>6580427</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,27 +1049,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hördes</t>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,69 +1071,69 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rikligt på en granlåga.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113563700</v>
+        <v>113722407</v>
       </c>
       <c r="B6" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gunnaretjärnet (Gunnaretjärnet), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352311</v>
+        <v>352418</v>
       </c>
       <c r="R6" t="n">
-        <v>6580169</v>
+        <v>6580190</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,22 +1157,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,30 +1179,26 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113563238</v>
+        <v>113722425</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,38 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stutögat (Stutögat), Vrm</t>
+          <t>Takenehöjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352418</v>
+        <v>352331</v>
       </c>
       <c r="R7" t="n">
-        <v>6580084</v>
+        <v>6580358</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,22 +1260,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,52 +1282,53 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Rikligt på basen av avbarkad björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113722408</v>
+        <v>113722460</v>
       </c>
       <c r="B8" t="n">
-        <v>94322</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>937</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352438</v>
+        <v>352305</v>
       </c>
       <c r="R8" t="n">
-        <v>6580149</v>
+        <v>6580420</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,12 +1368,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1472,6 +1389,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Måttligt på en grov asplåga</t>
+        </is>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
@@ -1489,37 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113722452</v>
+        <v>113722410</v>
       </c>
       <c r="B9" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352342</v>
+        <v>352423</v>
       </c>
       <c r="R9" t="n">
-        <v>6580459</v>
+        <v>6580113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,12 +1476,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1580,6 +1497,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Rikligt i en spricka på torraka</t>
+        </is>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
@@ -1597,37 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113722442</v>
+        <v>113722408</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352396</v>
+        <v>352438</v>
       </c>
       <c r="R10" t="n">
-        <v>6580478</v>
+        <v>6580149</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1667,12 +1584,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1688,11 +1605,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Rikligt på en tall.</t>
-        </is>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -1710,15 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113722441</v>
+        <v>113722377</v>
       </c>
       <c r="B11" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352369</v>
+        <v>352254</v>
       </c>
       <c r="R11" t="n">
-        <v>6580451</v>
+        <v>6580135</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1780,12 +1687,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1801,11 +1708,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Död.</t>
-        </is>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
@@ -1823,37 +1725,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113722436</v>
+        <v>113722450</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1863,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352243</v>
+        <v>352327</v>
       </c>
       <c r="R12" t="n">
-        <v>6580327</v>
+        <v>6580558</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,12 +1790,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1914,6 +1811,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på lodyta.</t>
+        </is>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
@@ -1931,37 +1833,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113722393</v>
+        <v>113722448</v>
       </c>
       <c r="B13" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352372</v>
+        <v>352332</v>
       </c>
       <c r="R13" t="n">
-        <v>6579963</v>
+        <v>6580580</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,12 +1898,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2022,6 +1919,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Måttligt/rikligt på lodyta.</t>
+        </is>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
@@ -2039,37 +1941,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113722424</v>
+        <v>113722438</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>352453</v>
+        <v>352246</v>
       </c>
       <c r="R14" t="n">
-        <v>6580363</v>
+        <v>6580468</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,12 +2006,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2130,6 +2027,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>40x30 cm</t>
+        </is>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
@@ -2147,37 +2049,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113722432</v>
+        <v>113722428</v>
       </c>
       <c r="B15" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>352271</v>
+        <v>352315</v>
       </c>
       <c r="R15" t="n">
-        <v>6580239</v>
+        <v>6580331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2255,37 +2152,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113722385</v>
+        <v>113722455</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>352307</v>
+        <v>352313</v>
       </c>
       <c r="R16" t="n">
-        <v>6580087</v>
+        <v>6580462</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2325,12 +2217,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2346,6 +2238,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>40x40 cm på granbas</t>
+        </is>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
@@ -2363,37 +2260,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113722383</v>
+        <v>113722417</v>
       </c>
       <c r="B17" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>352323</v>
+        <v>352491</v>
       </c>
       <c r="R17" t="n">
-        <v>6580089</v>
+        <v>6580318</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2433,12 +2325,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2471,15 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113722454</v>
+        <v>113722418</v>
       </c>
       <c r="B18" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,21 +2374,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>352310</v>
+        <v>352500</v>
       </c>
       <c r="R18" t="n">
-        <v>6580464</v>
+        <v>6580342</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2541,12 +2428,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2579,37 +2466,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113722458</v>
+        <v>113722433</v>
       </c>
       <c r="B19" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>352305</v>
+        <v>352189</v>
       </c>
       <c r="R19" t="n">
-        <v>6580429</v>
+        <v>6580274</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,12 +2531,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2670,11 +2552,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>20x5 cm på avbarkad granstubbe.</t>
-        </is>
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
@@ -2692,37 +2569,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113722390</v>
+        <v>113722381</v>
       </c>
       <c r="B20" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>352396</v>
+        <v>352325</v>
       </c>
       <c r="R20" t="n">
-        <v>6579980</v>
+        <v>6580086</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2783,11 +2655,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Små förekomster på asp</t>
-        </is>
       </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
@@ -2805,15 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113722457</v>
+        <v>113722440</v>
       </c>
       <c r="B21" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,21 +2683,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2845,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>352308</v>
+        <v>352315</v>
       </c>
       <c r="R21" t="n">
-        <v>6580435</v>
+        <v>6580409</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2899,7 +2761,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Flera blaffor på grov gran.</t>
+          <t>Måttligt på en granlåga.</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr"/>
@@ -2918,15 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113722445</v>
+        <v>113722444</v>
       </c>
       <c r="B22" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2958,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352445</v>
+        <v>352429</v>
       </c>
       <c r="R22" t="n">
-        <v>6580483</v>
+        <v>6580502</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3012,7 +2869,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Sparsamt på ett träd</t>
+          <t>Enstaka fruktkroppar på klen granlåga.</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr"/>
@@ -3031,15 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113722410</v>
+        <v>113722420</v>
       </c>
       <c r="B23" t="n">
-        <v>80429</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +2899,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>352423</v>
+        <v>352517</v>
       </c>
       <c r="R23" t="n">
-        <v>6580113</v>
+        <v>6580364</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,11 +2974,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Rikligt i en spricka på torraka</t>
-        </is>
       </c>
       <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
@@ -3144,15 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113722425</v>
+        <v>113722461</v>
       </c>
       <c r="B24" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,21 +3002,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>352331</v>
+        <v>352241</v>
       </c>
       <c r="R24" t="n">
-        <v>6580358</v>
+        <v>6580402</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,12 +3056,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3238,7 +3080,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Rikligt på basen av avbarkad björkhögstubbe.</t>
+          <t>En fruktkropp</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr"/>
@@ -3257,53 +3099,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113722448</v>
+        <v>113563238</v>
       </c>
       <c r="B25" t="n">
-        <v>94158</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Stutögat, Stutögat, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352332</v>
+        <v>352418</v>
       </c>
       <c r="R25" t="n">
-        <v>6580580</v>
+        <v>6580084</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3327,17 +3165,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3349,74 +3192,64 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Måttligt/rikligt på lodyta.</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113722386</v>
+        <v>113563373</v>
       </c>
       <c r="B26" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Gunnaretjärnet, Gunnaretjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352314</v>
+        <v>352393</v>
       </c>
       <c r="R26" t="n">
-        <v>6580018</v>
+        <v>6580236</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3440,17 +3273,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3462,74 +3300,64 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Tror den flög ut från bohål.</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113722460</v>
+        <v>113563389</v>
       </c>
       <c r="B27" t="n">
-        <v>89896</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>937</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Gunnaretjärnet, Gunnaretjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>352305</v>
+        <v>352394</v>
       </c>
       <c r="R27" t="n">
-        <v>6580420</v>
+        <v>6580301</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,17 +3381,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,36 +3408,25 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Måttligt på en grov asplåga</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr"/>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113722447</v>
+        <v>113720464</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,21 +3434,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>352353</v>
+        <v>352287</v>
       </c>
       <c r="R28" t="n">
-        <v>6580546</v>
+        <v>6580322</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3666,12 +3488,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3688,12 +3510,6 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>50 - 60 plantor uppskattningsvis, 2x2 m</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3702,44 +3518,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113722417</v>
+        <v>113722380</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3749,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>352491</v>
+        <v>352322</v>
       </c>
       <c r="R29" t="n">
-        <v>6580318</v>
+        <v>6580073</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,12 +3590,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3817,37 +3628,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113722414</v>
+        <v>113722385</v>
       </c>
       <c r="B30" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3857,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>352340</v>
+        <v>352307</v>
       </c>
       <c r="R30" t="n">
-        <v>6580195</v>
+        <v>6580087</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3887,12 +3693,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3925,37 +3731,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113722416</v>
+        <v>113722419</v>
       </c>
       <c r="B31" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3965,10 +3766,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>352444</v>
+        <v>352502</v>
       </c>
       <c r="R31" t="n">
-        <v>6580296</v>
+        <v>6580353</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,37 +3834,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113722381</v>
+        <v>113722421</v>
       </c>
       <c r="B32" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4073,10 +3869,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>352325</v>
+        <v>352508</v>
       </c>
       <c r="R32" t="n">
-        <v>6580086</v>
+        <v>6580378</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4103,12 +3899,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4141,37 +3937,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113722423</v>
+        <v>113722424</v>
       </c>
       <c r="B33" t="n">
-        <v>78758</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4181,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>352502</v>
+        <v>352453</v>
       </c>
       <c r="R33" t="n">
-        <v>6580383</v>
+        <v>6580363</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4249,19 +4040,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113720464</v>
+        <v>113722429</v>
       </c>
       <c r="B34" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4289,10 +4075,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>352287</v>
+        <v>352307</v>
       </c>
       <c r="R34" t="n">
-        <v>6580322</v>
+        <v>6580328</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4341,6 +4127,7 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4349,44 +4136,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Via Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113722444</v>
+        <v>113722436</v>
       </c>
       <c r="B35" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4396,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352429</v>
+        <v>352243</v>
       </c>
       <c r="R35" t="n">
-        <v>6580502</v>
+        <v>6580327</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4426,12 +4208,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4447,11 +4229,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar på klen granlåga.</t>
-        </is>
       </c>
       <c r="AR35" t="inlineStr"/>
       <c r="AT35" t="inlineStr"/>
@@ -4469,37 +4246,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113722412</v>
+        <v>113722437</v>
       </c>
       <c r="B36" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4509,10 +4281,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352455</v>
+        <v>352212</v>
       </c>
       <c r="R36" t="n">
-        <v>6580223</v>
+        <v>6580305</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4539,12 +4311,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4560,11 +4332,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Fin gammal asp.</t>
-        </is>
       </c>
       <c r="AR36" t="inlineStr"/>
       <c r="AT36" t="inlineStr"/>
@@ -4582,19 +4349,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113722429</v>
+        <v>113722439</v>
       </c>
       <c r="B37" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4622,10 +4384,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352307</v>
+        <v>352304</v>
       </c>
       <c r="R37" t="n">
-        <v>6580328</v>
+        <v>6580488</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4652,12 +4414,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4690,19 +4452,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113722421</v>
+        <v>113722442</v>
       </c>
       <c r="B38" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4730,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>352508</v>
+        <v>352396</v>
       </c>
       <c r="R38" t="n">
-        <v>6580378</v>
+        <v>6580478</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4760,12 +4517,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4781,6 +4538,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Rikligt på en tall.</t>
+        </is>
       </c>
       <c r="AR38" t="inlineStr"/>
       <c r="AT38" t="inlineStr"/>
@@ -4798,32 +4560,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113722415</v>
+        <v>113722453</v>
       </c>
       <c r="B39" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4838,10 +4595,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352372</v>
+        <v>352312</v>
       </c>
       <c r="R39" t="n">
-        <v>6580292</v>
+        <v>6580470</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4868,12 +4625,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4889,6 +4646,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Rikliga mängder på senvuxen gran.</t>
+        </is>
       </c>
       <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
@@ -4906,53 +4668,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113722392</v>
+        <v>113563700</v>
       </c>
       <c r="B40" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Gunnaretjärnet, Gunnaretjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352398</v>
+        <v>352311</v>
       </c>
       <c r="R40" t="n">
-        <v>6579956</v>
+        <v>6580169</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4976,17 +4734,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4998,31 +4761,25 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AR40" t="inlineStr"/>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113722409</v>
+        <v>113722378</v>
       </c>
       <c r="B41" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,21 +4787,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5054,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>352428</v>
+        <v>352266</v>
       </c>
       <c r="R41" t="n">
-        <v>6580131</v>
+        <v>6580137</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5084,12 +4841,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5105,6 +4862,11 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Rikligt på varje gran.</t>
+        </is>
       </c>
       <c r="AR41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
@@ -5122,15 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113722453</v>
+        <v>113722382</v>
       </c>
       <c r="B42" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,21 +4895,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5162,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352312</v>
+        <v>352320</v>
       </c>
       <c r="R42" t="n">
-        <v>6580470</v>
+        <v>6580092</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5192,12 +4949,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5213,11 +4970,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Rikliga mängder på senvuxen gran.</t>
-        </is>
       </c>
       <c r="AR42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
@@ -5235,37 +4987,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113722428</v>
+        <v>113722389</v>
       </c>
       <c r="B43" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352315</v>
+        <v>352358</v>
       </c>
       <c r="R43" t="n">
-        <v>6580331</v>
+        <v>6580002</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5305,12 +5052,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5343,37 +5090,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113722434</v>
+        <v>113722394</v>
       </c>
       <c r="B44" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5383,10 +5125,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>352204</v>
+        <v>352318</v>
       </c>
       <c r="R44" t="n">
-        <v>6580301</v>
+        <v>6579944</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5413,12 +5155,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5451,37 +5193,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113722431</v>
+        <v>113722414</v>
       </c>
       <c r="B45" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5491,10 +5228,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>352259</v>
+        <v>352340</v>
       </c>
       <c r="R45" t="n">
-        <v>6580252</v>
+        <v>6580195</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5559,15 +5296,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113722461</v>
+        <v>113722422</v>
       </c>
       <c r="B46" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5575,21 +5307,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5599,10 +5331,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>352241</v>
+        <v>352517</v>
       </c>
       <c r="R46" t="n">
-        <v>6580402</v>
+        <v>6580382</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5629,12 +5361,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5650,11 +5382,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>En fruktkropp</t>
-        </is>
       </c>
       <c r="AR46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
@@ -5672,15 +5399,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113722384</v>
+        <v>113722427</v>
       </c>
       <c r="B47" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5410,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5712,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>352311</v>
+        <v>352325</v>
       </c>
       <c r="R47" t="n">
-        <v>6580063</v>
+        <v>6580351</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5742,12 +5464,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5763,11 +5485,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Rikligt på klen tallraka</t>
-        </is>
       </c>
       <c r="AR47" t="inlineStr"/>
       <c r="AT47" t="inlineStr"/>
@@ -5785,15 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113722391</v>
+        <v>113722430</v>
       </c>
       <c r="B48" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5801,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5825,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352404</v>
+        <v>352311</v>
       </c>
       <c r="R48" t="n">
-        <v>6579983</v>
+        <v>6580343</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5855,12 +5567,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5876,11 +5588,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Små förekomster på asp</t>
-        </is>
       </c>
       <c r="AR48" t="inlineStr"/>
       <c r="AT48" t="inlineStr"/>
@@ -5898,37 +5605,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113722450</v>
+        <v>113722445</v>
       </c>
       <c r="B49" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2666</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5938,10 +5640,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352327</v>
+        <v>352445</v>
       </c>
       <c r="R49" t="n">
-        <v>6580558</v>
+        <v>6580483</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5992,7 +5694,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Mycket rikligt på lodyta.</t>
+          <t>Sparsamt på ett träd</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr"/>
@@ -6011,37 +5713,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113722455</v>
+        <v>113722452</v>
       </c>
       <c r="B50" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6051,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352313</v>
+        <v>352342</v>
       </c>
       <c r="R50" t="n">
-        <v>6580462</v>
+        <v>6580459</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6102,11 +5799,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>40x40 cm på granbas</t>
-        </is>
       </c>
       <c r="AR50" t="inlineStr"/>
       <c r="AT50" t="inlineStr"/>
@@ -6124,37 +5816,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113722435</v>
+        <v>113722456</v>
       </c>
       <c r="B51" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6164,10 +5851,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352209</v>
+        <v>352313</v>
       </c>
       <c r="R51" t="n">
-        <v>6580310</v>
+        <v>6580462</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6194,12 +5881,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6232,37 +5919,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113722443</v>
+        <v>113722457</v>
       </c>
       <c r="B52" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6272,10 +5954,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352386</v>
+        <v>352308</v>
       </c>
       <c r="R52" t="n">
-        <v>6580499</v>
+        <v>6580435</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6326,7 +6008,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Små förekomster på en asp</t>
+          <t>Flera blaffor på grov gran.</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr"/>
@@ -6345,15 +6027,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113722433</v>
+        <v>113722451</v>
       </c>
       <c r="B53" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6361,21 +6038,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6428</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6385,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>352189</v>
+        <v>352360</v>
       </c>
       <c r="R53" t="n">
-        <v>6580274</v>
+        <v>6580500</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6415,12 +6092,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6436,6 +6113,11 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Rikligt på alstubbe</t>
+        </is>
       </c>
       <c r="AR53" t="inlineStr"/>
       <c r="AT53" t="inlineStr"/>
@@ -6453,15 +6135,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113722438</v>
+        <v>113722434</v>
       </c>
       <c r="B54" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6469,21 +6146,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2809</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6493,10 +6170,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>352246</v>
+        <v>352204</v>
       </c>
       <c r="R54" t="n">
-        <v>6580468</v>
+        <v>6580301</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6523,12 +6200,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6544,11 +6221,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>40x30 cm</t>
-        </is>
       </c>
       <c r="AR54" t="inlineStr"/>
       <c r="AT54" t="inlineStr"/>
@@ -6566,15 +6238,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113722380</v>
+        <v>113722384</v>
       </c>
       <c r="B55" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6582,21 +6249,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6606,10 +6273,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>352322</v>
+        <v>352311</v>
       </c>
       <c r="R55" t="n">
-        <v>6580073</v>
+        <v>6580063</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6657,6 +6324,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Rikligt på klen tallraka</t>
+        </is>
       </c>
       <c r="AR55" t="inlineStr"/>
       <c r="AT55" t="inlineStr"/>
@@ -6674,15 +6346,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113722456</v>
+        <v>113722379</v>
       </c>
       <c r="B56" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6690,21 +6357,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>6439</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6714,10 +6381,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>352313</v>
+        <v>352326</v>
       </c>
       <c r="R56" t="n">
-        <v>6580462</v>
+        <v>6580136</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6744,12 +6411,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6782,37 +6449,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113722459</v>
+        <v>113722431</v>
       </c>
       <c r="B57" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6822,10 +6484,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>352309</v>
+        <v>352259</v>
       </c>
       <c r="R57" t="n">
-        <v>6580427</v>
+        <v>6580252</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6852,12 +6514,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6873,11 +6535,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Rikligt på en granlåga.</t>
-        </is>
       </c>
       <c r="AR57" t="inlineStr"/>
       <c r="AT57" t="inlineStr"/>
@@ -6895,15 +6552,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113722426</v>
+        <v>113722458</v>
       </c>
       <c r="B58" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,21 +6563,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106554</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6935,10 +6587,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352331</v>
+        <v>352305</v>
       </c>
       <c r="R58" t="n">
-        <v>6580360</v>
+        <v>6580429</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6965,12 +6617,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6986,6 +6638,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>20x5 cm på avbarkad granstubbe.</t>
+        </is>
       </c>
       <c r="AR58" t="inlineStr"/>
       <c r="AT58" t="inlineStr"/>
@@ -7003,15 +6660,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113722407</v>
+        <v>113722416</v>
       </c>
       <c r="B59" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7019,21 +6671,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7043,10 +6695,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>352418</v>
+        <v>352444</v>
       </c>
       <c r="R59" t="n">
-        <v>6580190</v>
+        <v>6580296</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7111,37 +6763,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113722440</v>
+        <v>113722432</v>
       </c>
       <c r="B60" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7151,10 +6798,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352315</v>
+        <v>352271</v>
       </c>
       <c r="R60" t="n">
-        <v>6580409</v>
+        <v>6580239</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7181,12 +6828,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7202,11 +6849,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Måttligt på en granlåga.</t>
-        </is>
       </c>
       <c r="AR60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
@@ -7224,37 +6866,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113722427</v>
+        <v>113722390</v>
       </c>
       <c r="B61" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7264,10 +6901,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352325</v>
+        <v>352396</v>
       </c>
       <c r="R61" t="n">
-        <v>6580351</v>
+        <v>6579980</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7294,12 +6931,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7315,6 +6952,11 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Små förekomster på asp</t>
+        </is>
       </c>
       <c r="AR61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
@@ -7332,15 +6974,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113722439</v>
+        <v>113722391</v>
       </c>
       <c r="B62" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7348,21 +6985,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7372,10 +7009,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>352304</v>
+        <v>352404</v>
       </c>
       <c r="R62" t="n">
-        <v>6580488</v>
+        <v>6579983</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7402,12 +7039,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7423,6 +7060,11 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Små förekomster på asp</t>
+        </is>
       </c>
       <c r="AR62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
@@ -7440,15 +7082,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113722430</v>
+        <v>113722423</v>
       </c>
       <c r="B63" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7456,21 +7093,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6426</v>
+        <v>6459</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7480,10 +7117,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>352311</v>
+        <v>352502</v>
       </c>
       <c r="R63" t="n">
-        <v>6580343</v>
+        <v>6580383</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7548,15 +7185,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113722389</v>
+        <v>113722415</v>
       </c>
       <c r="B64" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7564,21 +7196,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7588,10 +7220,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>352358</v>
+        <v>352372</v>
       </c>
       <c r="R64" t="n">
-        <v>6580002</v>
+        <v>6580292</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7618,12 +7250,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7656,15 +7288,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113722379</v>
+        <v>113722443</v>
       </c>
       <c r="B65" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,21 +7299,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7696,10 +7323,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>352326</v>
+        <v>352386</v>
       </c>
       <c r="R65" t="n">
-        <v>6580136</v>
+        <v>6580499</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7726,12 +7353,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7747,6 +7374,11 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Små förekomster på en asp</t>
+        </is>
       </c>
       <c r="AR65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
@@ -7764,32 +7396,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113722446</v>
+        <v>113722386</v>
       </c>
       <c r="B66" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7804,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>352398</v>
+        <v>352314</v>
       </c>
       <c r="R66" t="n">
-        <v>6580555</v>
+        <v>6580018</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7834,12 +7461,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7858,7 +7485,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Tror den flög ut från bohål.</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr"/>
@@ -7877,15 +7504,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113722419</v>
+        <v>113722446</v>
       </c>
       <c r="B67" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7893,21 +7515,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7917,10 +7539,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>352502</v>
+        <v>352398</v>
       </c>
       <c r="R67" t="n">
-        <v>6580353</v>
+        <v>6580555</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7947,12 +7569,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -7968,6 +7590,11 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
       </c>
       <c r="AR67" t="inlineStr"/>
       <c r="AT67" t="inlineStr"/>
@@ -7985,15 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113722418</v>
+        <v>113722441</v>
       </c>
       <c r="B68" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8001,21 +7623,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8025,10 +7647,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>352500</v>
+        <v>352369</v>
       </c>
       <c r="R68" t="n">
-        <v>6580342</v>
+        <v>6580451</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8055,12 +7677,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8076,6 +7698,11 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Död.</t>
+        </is>
       </c>
       <c r="AR68" t="inlineStr"/>
       <c r="AT68" t="inlineStr"/>
@@ -8093,37 +7720,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113722437</v>
+        <v>113722383</v>
       </c>
       <c r="B69" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8133,10 +7755,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>352212</v>
+        <v>352323</v>
       </c>
       <c r="R69" t="n">
-        <v>6580305</v>
+        <v>6580089</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8163,12 +7785,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8201,53 +7823,58 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113722394</v>
+        <v>113563144</v>
       </c>
       <c r="B70" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Stutögat, Stutögat, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>352318</v>
+        <v>352367</v>
       </c>
       <c r="R70" t="n">
-        <v>6579944</v>
+        <v>6579883</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8271,17 +7898,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>Hördes</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8293,66 +7930,70 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AR70" t="inlineStr"/>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113722382</v>
+        <v>113563468</v>
       </c>
       <c r="B71" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Takenehöjden, Vrm</t>
+          <t>Myggedalen, Myggedalen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>352320</v>
+        <v>352554</v>
       </c>
       <c r="R71" t="n">
-        <v>6580092</v>
+        <v>6580561</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,17 +8020,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>JMN0109 Takenehöjden NVI</t>
+          <t>Hördes</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8401,31 +8052,25 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AR71" t="inlineStr"/>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Jonas Mattsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113722451</v>
+        <v>113722426</v>
       </c>
       <c r="B72" t="n">
-        <v>74459</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8433,21 +8078,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6428</v>
+        <v>106554</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8457,10 +8102,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352360</v>
+        <v>352331</v>
       </c>
       <c r="R72" t="n">
-        <v>6580500</v>
+        <v>6580360</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8487,12 +8132,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8508,11 +8153,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Rikligt på alstubbe</t>
-        </is>
       </c>
       <c r="AR72" t="inlineStr"/>
       <c r="AT72" t="inlineStr"/>
@@ -8530,15 +8170,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113722422</v>
+        <v>113722435</v>
       </c>
       <c r="B73" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8546,21 +8181,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8570,10 +8205,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352517</v>
+        <v>352209</v>
       </c>
       <c r="R73" t="n">
-        <v>6580382</v>
+        <v>6580310</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8638,15 +8273,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113722387</v>
+        <v>113722449</v>
       </c>
       <c r="B74" t="n">
-        <v>80109</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8654,21 +8284,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230185</v>
+        <v>106554</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8678,10 +8308,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>352317</v>
+        <v>352306</v>
       </c>
       <c r="R74" t="n">
-        <v>6580024</v>
+        <v>6580537</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8708,12 +8338,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8732,7 +8362,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Måttlig förekomst på klibbal</t>
+          <t>Rikligt med gnag på en gammal björklåga.</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr"/>
@@ -8748,6 +8378,536 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>113722447</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Takenehöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>352353</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6580546</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>50 - 60 plantor uppskattningsvis, 2x2 m</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Via Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>113722392</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Takenehöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>352398</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6579956</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Via Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>113722411</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Takenehöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>352474</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6580191</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Via Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>113722412</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Takenehöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>352455</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6580223</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Fin gammal asp.</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Via Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>113722387</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Takenehöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>352317</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6580024</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>JMN0109 Takenehöjden NVI</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst på klibbal</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Via Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
